--- a/business_surveys/040_global_market_insights_survey_form--business_surveys.xlsx
+++ b/business_surveys/040_global_market_insights_survey_form--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_d</t>
+          <t>option d</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_e</t>
+          <t>option e</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_f</t>
+          <t>option f</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_g</t>
+          <t>option g</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_h</t>
+          <t>option h</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_i</t>
+          <t>option i</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_j</t>
+          <t>option j</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_k</t>
+          <t>option k</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_l</t>
+          <t>option l</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_m</t>
+          <t>option m</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_n</t>
+          <t>option n</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_o</t>
+          <t>option o</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_p</t>
+          <t>option p</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_q</t>
+          <t>option q</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_r</t>
+          <t>option r</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_s</t>
+          <t>option s</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_t</t>
+          <t>option t</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_u</t>
+          <t>option u</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_v</t>
+          <t>option v</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_w</t>
+          <t>option w</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option_x</t>
+          <t>option x</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option_y</t>
+          <t>option y</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option_z</t>
+          <t>option z</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option_aa</t>
+          <t>option aa</t>
         </is>
       </c>
     </row>
